--- a/Aerosol/Aerosol_Job_Card.xlsx
+++ b/Aerosol/Aerosol_Job_Card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\Aerosol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745ADFE5-A348-466A-969B-0DE78FC4108E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD02961-A13A-4F68-AAAC-17AEED2A9995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,6 +697,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -736,12 +742,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,26 +1090,26 @@
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" customWidth="1"/>
+    <col min="3" max="3" width="48.7109375" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
       <c r="E2" t="s">
         <v>2</v>
       </c>
@@ -1120,14 +1120,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1184,14 +1184,14 @@
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -1839,14 +1839,14 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -1941,14 +1941,14 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
@@ -1960,48 +1960,48 @@
       <c r="C45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="19"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="23"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="21"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="25"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="23"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="25"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F48"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
